--- a/artfynd/A 26467-2024 artfynd.xlsx
+++ b/artfynd/A 26467-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>16801441</v>
       </c>
       <c r="B2" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598126.6603916243</v>
+        <v>598127</v>
       </c>
       <c r="R2" t="n">
-        <v>7032996.465330977</v>
+        <v>7032996</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2014-07-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-07-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97528245</v>
+        <v>16072276</v>
       </c>
       <c r="B3" t="n">
-        <v>95521</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,30 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224363</v>
+        <v>2082</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jättjärnsbäcken, Ång</t>
+          <t>Jättjärnsbäcken vid Storbrännan, Lidgatu, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598097.1370986555</v>
+        <v>598114</v>
       </c>
       <c r="R3" t="n">
-        <v>7032978.525854138</v>
+        <v>7033005</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-07-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-07-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,33 +861,28 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Invid bäck i fuktig och tuvig mark i utkanten av gammal skog</t>
+          <t>gransumpskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Anders Svenson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Åke Svensson, Erik Ljungstrand</t>
+          <t>Anders Svenson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97528254</v>
+        <v>16801439</v>
       </c>
       <c r="B4" t="n">
-        <v>103088</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,34 +890,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221101</v>
+        <v>2082</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jättjärnsbäcken, Ång</t>
+          <t>Jättjärnsbäcken, Lidgatu, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598097.1370986555</v>
+        <v>598127</v>
       </c>
       <c r="R4" t="n">
-        <v>7032978.525854138</v>
+        <v>7033000</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,27 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-07-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>i blom</t>
+          <t>2014-07-05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,18 +968,18 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Invid bäck i fuktig och tuvig mark i utkanten av gammal skog</t>
+          <t>Sumpig/fuktig skog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Åke Svensson, Erik Ljungstrand</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1030,12 +989,7 @@
         <v>97528250</v>
       </c>
       <c r="B5" t="n">
-        <v>97552</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598097.1370986555</v>
+        <v>598097</v>
       </c>
       <c r="R5" t="n">
-        <v>7032978.525854138</v>
+        <v>7032979</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,19 +1063,9 @@
           <t>2021-07-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-07-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1155,6 +1099,322 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>97879010</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100387</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Jättjärnsbäcken vid Storbrännan, Lidgatu, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>598117</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7033006</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2014-07-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2014-07-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>SBF:s botanikdagar</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lars Erik Norbäck</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars Erik Norbäck</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>97528254</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106061</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221101</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Springkorn</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Impatiens noli-tangere</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Jättjärnsbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>598097</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7032979</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-07-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-07-22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>i blom</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Invid bäck i fuktig och tuvig mark i utkanten av gammal skog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo, Åke Svensson, Erik Ljungstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>97528245</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Jättjärnsbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>598097</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7032979</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-07-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-07-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Invid bäck i fuktig och tuvig mark i utkanten av gammal skog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo, Åke Svensson, Erik Ljungstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26467-2024 artfynd.xlsx
+++ b/artfynd/A 26467-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16801441</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16072276</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16801439</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97528250</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97879010</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1317,6 +1347,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97528254</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1415,8 +1450,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97528245</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>